--- a/uploads/boq_temp.xlsx
+++ b/uploads/boq_temp.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\polman\semester 6\PPI EXTERNAL\MATERIAL RECAP AND CUTTING PLAN\PAK JERI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\polman\semester 6\PPI EXTERNAL\cutting_plan\cutting-plan-ffd\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E769A5B4-E3BF-4EB2-B831-538C360E74FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EC4D069B-C6E0-498C-A781-4CB2F65D0062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{726FDF11-35A9-49B7-A54B-D5667343F664}"/>
   </bookViews>
